--- a/docs/StructureDefinition-NoImplVitalSignsObservationQSOFAScore.xlsx
+++ b/docs/StructureDefinition-NoImplVitalSignsObservationQSOFAScore.xlsx
@@ -1302,7 +1302,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://dips.no/fhir/R4/StructureDefinition/DIPSPatient)
+    <t xml:space="preserve">Reference(http://dips.no/fhir/StructureDefinition/R4/DIPSPatient)
 </t>
   </si>
   <si>
